--- a/TESTS/zlit_6_london.xlsx
+++ b/TESTS/zlit_6_london.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -561,6 +561,11 @@
           <t>Тип</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ГР</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -580,7 +585,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Джек Лондон — американський письменник відомий творами про Північ і виживання людини в екстремальних умовах</t>
+          <t>Джек Лондон</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -601,6 +606,11 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -622,7 +632,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>На канадській Півночі — в холодній арктичній тундрі де людина залишається один на один з природою</t>
+          <t>На канадській Півночі</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -643,6 +653,11 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -687,6 +702,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -706,7 +726,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Білл покинув пораненого героя рятуючись сам — зрада в критичній ситуації що посилює самотність героя</t>
+          <t>Білл покинув пораненого героя рятуючись сам</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -727,6 +747,11 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -748,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Голод виснаження і вовк що переслідує його — постійна боротьба між життям і смертю</t>
+          <t>Голод виснаження і вовк що переслідує його</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -769,6 +794,11 @@
       <c r="H6" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -790,7 +820,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Хворий виснажений вовк — між ними дивне суперництво двох приречених що боряться за виживання</t>
+          <t>Хворий виснажений вовк</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -811,6 +841,11 @@
       <c r="H7" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -832,7 +867,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>На межі смерті — не може ходити і повзе до моря куди інстинкт самозбереження веде його</t>
+          <t>На межі смерті</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -853,6 +888,11 @@
       <c r="H8" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -874,7 +914,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Він надто знесилений щоб навіть зреагувати — лише інстинктивне повзання тримає його живим</t>
+          <t>Він надто знесилений щоб навіть зреагувати</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -895,6 +935,11 @@
       <c r="H9" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -916,7 +961,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Хто кого переживе — обидва настільки слабкі що лише воля до життя вирішує хто виживе</t>
+          <t>Хто кого переживе</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -937,6 +982,11 @@
       <c r="H10" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -948,37 +998,42 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 1)</t>
+          <t>Чим займались герой і Білл на Півночі перед тим, як опинились у скруті?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Полювали для розваги</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Шукали золото разом з іншими членами експедиції</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Досліджували карту</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Втікали від поліції</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -990,37 +1045,42 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 2)</t>
+          <t>Що сталося з рештою членів експедиції, перш ніж герой залишився сам із Біллом?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Усі загинули одночасно</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вони розділилися, і герой із Біллом залишились останніми двома</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Усі повернулись додому</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Їх ніколи не було</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1032,37 +1092,42 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 3)</t>
+          <t>Куди прямували герой і Білл, коли стався нещасний випадок?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>До найближчого міста</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>До факторії на берегу річки, де чекали запаси й допомога</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>До гір за золотом</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Назад, тим самим шляхом</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1074,37 +1139,42 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 1)</t>
+          <t>Як герой пошкодив ногу?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Його вкусила змія</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Підвернув і поранив ногу, перестрибуючи через каміння в річці</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Його вкусив вовк</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Впав з коня</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1116,37 +1186,42 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 2)</t>
+          <t>Як травма ноги впливала на швидкість пересування героя?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Не впливала зовсім</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Сильно сповільнювала його, змушуючи відставати від Білла</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він зовсім не міг рухатись</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Лише вночі боліла</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1158,37 +1233,42 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 3)</t>
+          <t>Чому Білл не міг довго чекати на героя з пораненою ногою?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Білл не хотів чекати з жорстокості</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Запасів їжі було мало на двох, і затримка загрожувала смертю обом</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Білл боявся темряви</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Білл захворів сам</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1200,37 +1280,42 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 1)</t>
+          <t>Чим переважно харчувався герой, коли скінчились останні запаси?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>М'ясом тварин, яких ловив</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Болотяними ягодами та водяними кореневищами, яких міг знайти</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Рибою з річки</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Нічим, голодував повністю</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1242,37 +1327,42 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 2)</t>
+          <t>Що герой пробував робити, аби здобути хоч якесь м'ясо?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Просив у духів</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Намагався ловити куріпок і дрібну дичину голіруч чи камінням, здебільшого невдало</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Розвів вогнище для приманки</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Викопав пастку для ведмедя</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1284,37 +1374,42 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 3)</t>
+          <t>Що герой зробив із кістками, знайденими біля старого табору?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Викинув їх</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Розгризав і смоктав їх, видобуваючи останні залишки живлення</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Поховав їх</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Зробив з них зброю</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1326,37 +1421,42 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 1)</t>
+          <t>Що почав відчувати герой через сильне виснаження і голод?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він став сильнішим</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>У нього почалися видіння, межа між реальністю і маренням стиралась</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він заспокоївся</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він заснув надовго і не прокидався</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1368,37 +1468,42 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 2)</t>
+          <t>Що герой почав робити з частиною свого спорядження через виснаження?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Беріг кожну річ</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Поступово кидав по дорозі все, що вважав зайвим тягарем, навіть цінні речі</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Загубив усе одразу</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Продав усе</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1410,37 +1515,42 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 3)</t>
+          <t>Як змінювалось сприйняття героєм часу і відстані під час подорожі?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він точно знав, скільки пройшов</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Він втрачав відчуття часу і відстані, рухаючись майже механічно, повзучи останніми силами</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Час минав швидше, ніж зазвичай</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він зупинився рахувати кроки</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1452,37 +1562,42 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 1)</t>
+          <t>Кого герой побачив, вибравшись на узвишшя, виснажений до краю?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Людей</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Велике стадо карибу (диких оленів), що проходило повз</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Ведмедя</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Корабель</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1494,37 +1609,42 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 2)</t>
+          <t>Чи вдалося героєві здобути м'ясо з цього стада карибу?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Так, легко</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Ні — він був занадто слабким, щоб полювати, і стадо пройшло мимо</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Стадо саме підійшло до нього</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він застрелив одного оленя</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1536,37 +1656,42 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 3)</t>
+          <t>Що, окрім стада оленів, постійно йшло слідом за виснаженим героєм, чекаючи на його смерть?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Ворон</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Хворий, слабкий вовк</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Інша людина</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Ведмідь</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1578,37 +1703,42 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 1)</t>
+          <t>Що герой знайшов на своєму шляху, що належало Біллу, який пішов уперед сам?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Записку від Білла</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Розкидані кістки — останки Білла, з'їденого вовками, і мішечок із золотим піском поруч</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Слід Білла, що веде далі</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Самого живого Білла</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1620,37 +1750,42 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 2)</t>
+          <t>Що герой зробив, побачивши мішечок із золотом біля кісток Білла?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Одразу забрав його із собою, незважаючи на вагу</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Спершу думав узяти, але зрештою кинув золото — воно стало йому байдужим перед загрозою смерті</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Закопав золото</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Поділив його навпіл</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1662,37 +1797,42 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 3)</t>
+          <t>Як знахідка останків Білла вплинула на героя?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він зрадів, що Білл мертвий</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Це стало ще одним нагадуванням про тонку межу між життям і смертю в дикій природі</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він одразу здався і ліг помирати</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він пішов його ховати</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1704,37 +1844,42 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 1)</t>
+          <t>Хто врешті врятував героя, коли він уже повз берегом моря?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Місцеві мисливці</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Моряки з наукового судна «Бедфорд», що випадково помітили його з моря</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Білл, який вижив</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Поліція</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1746,37 +1891,42 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 2)</t>
+          <t>Як герой повів себе з їжею вже на борту корабля, попри те, що тепер їжі було вдосталь?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Їв спокійно, як усі</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Тайкома ховав хліб під подушкою чи одягом, попри те, що їжі вже вистачало</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Відмовлявся їсти</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Роздавав їжу іншим</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1788,37 +1938,42 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 3)</t>
+          <t>Чому, на думку інших на кораблі, герой поводився так дивно з їжею навіть після порятунку?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він був жадібним за натурою</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Пережитий смертельний голод залишив глибокий психологічний слід, який не зник одразу з порятунком</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він готувався до нової подорожі</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він не довіряв морякам</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1843,8 +1998,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>Б</t>
@@ -1853,6 +2006,11 @@
       <c r="H32" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1877,8 +2035,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>А</t>
@@ -1887,6 +2043,11 @@
       <c r="H33" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1911,8 +2072,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>А</t>
@@ -1921,6 +2080,11 @@
       <c r="H34" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1932,21 +2096,19 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Який стиль письма Джека Лондона виявляється в «Жазі до життя»?</t>
+          <t>Стиль Джека Лондона у «Жазі до життя» — стриманий, насичений деталями виживання, без зайвої сентиментальності.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>А</t>
@@ -1955,6 +2117,11 @@
       <c r="H35" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1966,21 +2133,19 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Яка філософія виявляється в творчості Джека Лондона?</t>
+          <t>У творчості Джека Лондона часто звучить тема боротьби людини за існування в суворих природних умовах.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>А</t>
@@ -1989,6 +2154,11 @@
       <c r="H36" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2000,29 +2170,32 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Що спільного між творами Джека Лондона і літературою про виживання?</t>
+          <t>«Жага до життя» не має нічого спільного з пізнішою літературою про виживання в дикій природі.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2034,21 +2207,19 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Чим закінчується оповідання «Жага до життя»?</t>
+          <t>Оповідання закінчується тим, що героя рятують моряки з корабля «Бедфорд».</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>А</t>
@@ -2057,6 +2228,11 @@
       <c r="H38" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2068,29 +2244,32 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Яка деталь показує психологічну травму героя після порятунку?</t>
+          <t>Звичка героя ховати їжу навіть після порятунку свідчить про те, що він не довіряв морякам і боявся отруєння.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2102,21 +2281,19 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Яка головна ідея оповідання «Жага до життя»?</t>
+          <t>Головна ідея оповідання — навіть у межовій ситуації воля до життя здатна перемогти відчай і смерть.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
           <t>А</t>
@@ -2125,6 +2302,11 @@
       <c r="H40" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2169,6 +2351,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2211,6 +2398,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2220,27 +2412,27 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Які ресурси виживання використовує герой в оповіданні?</t>
+          <t>Що сталося з героєм під час подорожі?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Фізична витривалість</t>
+          <t>Знайшов кістки Білла</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Інстинкт самозбереження</t>
+          <t>Повз ним пройшло стадо карибу</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Магічні сили</t>
+          <t>Вовк допоміг йому дійти до моря</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Воля до життя попри відчай</t>
+          <t>Його врятували моряки</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2251,6 +2443,11 @@
       <c r="H43" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2469,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Саму смерть що чекає — але і дзеркало героя: обидва хворі обидва борються обидва не здаються</t>
+          <t>Саму смерть що чекає</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2293,6 +2490,11 @@
       <c r="H44" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2516,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Воля до життя — спільна для людини і тварини — і в цьому двобої перемагає той у кого вона сильніша</t>
+          <t>Воля до життя</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2335,6 +2537,11 @@
       <c r="H45" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2563,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Після довгого виснажливого протистояння герой кусає вовка і п'є його кров — перемагає інстинктом</t>
+          <t>Після довгого виснажливого протистояння герой кусає вовка і п'є його кров</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2377,6 +2584,11 @@
       <c r="H46" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
